--- a/Platform/Platform.WebSite/ModuleResources/Other/Supplier/新增供應商匯入範本.xlsx
+++ b/Platform/Platform.WebSite/ModuleResources/Other/Supplier/新增供應商匯入範本.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nkp07\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nkp07\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{189D0DE0-43F5-4E5F-9A35-CD19B8E85A6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{434CEB2E-E7A8-4E54-B122-4086BE56AB31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9CCFBBE6-BC22-49C3-84C8-F09A8799A7EF}"/>
   </bookViews>
@@ -1423,6 +1423,123 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>國內銀行3碼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>國內分行4碼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>帳號請去除"-"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="5"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+      </rPr>
+      <t>欄位值必須為
+台灣、日本、美國</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="5"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+      </rPr>
+      <t>欄位值必須為</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="5"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>NTD</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="5"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+      </rPr>
+      <t>、</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="5"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>JPY</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="5"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+      </rPr>
+      <t>、</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="5"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>USD</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>外幣帳戶請填英文帳戶名稱</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>請填寫英文地址</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>請填寫城市英文名稱</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>外幣帳戶必填</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>若為外幣匯款，請以英文填寫公司地址</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <r>
       <t>1.</t>
     </r>
@@ -1502,7 +1619,7 @@
         <rFont val="Times New Roman"/>
         <family val="1"/>
       </rPr>
-      <t xml:space="preserve">/ PQM </t>
+      <t xml:space="preserve">/ SCM </t>
     </r>
     <r>
       <rPr>
@@ -1522,7 +1639,7 @@
         <family val="1"/>
       </rPr>
       <t xml:space="preserve"> &lt;yuka.chang@tel.com&gt;
-   All supplier will need to provide the signature of ' Letter of Undertaking for Code of Conduct' and seed the reserved copy to SRI Yuka&lt;yuka.chang@tel.com&gt;
+   All supplier will need to provide the signature of ' Letter of Undertaking for Code of Conduct' and seed the reserved copy to SCM Yuka&lt;yuka.chang@tel.com&gt;
 3.</t>
     </r>
     <r>
@@ -1533,7 +1650,7 @@
         <family val="1"/>
         <charset val="136"/>
       </rPr>
-      <t xml:space="preserve">勞務及廠務工程承攬商請務必填寫《承攬商安全衛生環保承諾書》
+      <t xml:space="preserve">勞務及廠務工程承攬商請務必填寫《承攬商安全衛生環保規章保證書》
 </t>
     </r>
     <r>
@@ -1565,123 +1682,6 @@
       </rPr>
       <t>為必填欄位</t>
     </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>國內銀行3碼</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>國內分行4碼</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>帳號請去除"-"</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="5"/>
-        <rFont val="新細明體"/>
-        <family val="1"/>
-        <charset val="136"/>
-      </rPr>
-      <t>欄位值必須為
-台灣、日本、美國</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="5"/>
-        <rFont val="新細明體"/>
-        <family val="1"/>
-        <charset val="136"/>
-      </rPr>
-      <t>欄位值必須為</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="5"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>NTD</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="5"/>
-        <rFont val="新細明體"/>
-        <family val="1"/>
-        <charset val="136"/>
-      </rPr>
-      <t>、</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="5"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>JPY</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="5"/>
-        <rFont val="新細明體"/>
-        <family val="1"/>
-        <charset val="136"/>
-      </rPr>
-      <t>、</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="5"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>USD</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>外幣帳戶請填英文帳戶名稱</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>請填寫英文地址</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>請填寫城市英文名稱</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>外幣帳戶必填</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>若為外幣匯款，請以英文填寫公司地址</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2896,6 +2896,9 @@
     <xf numFmtId="49" fontId="21" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="11" fillId="0" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2982,9 +2985,6 @@
     </xf>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="58" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3472,31 +3472,31 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:7" ht="52.5" customHeight="1">
-      <c r="B2" s="52" t="s">
+      <c r="B2" s="53" t="s">
         <v>28</v>
       </c>
-      <c r="C2" s="53"/>
-      <c r="D2" s="53"/>
-      <c r="E2" s="53"/>
-      <c r="F2" s="53"/>
-      <c r="G2" s="54"/>
+      <c r="C2" s="54"/>
+      <c r="D2" s="54"/>
+      <c r="E2" s="54"/>
+      <c r="F2" s="54"/>
+      <c r="G2" s="55"/>
     </row>
     <row r="3" spans="1:7" ht="120" customHeight="1" thickBot="1">
-      <c r="B3" s="77" t="s">
-        <v>39</v>
-      </c>
-      <c r="C3" s="78"/>
-      <c r="D3" s="78"/>
-      <c r="E3" s="78"/>
-      <c r="F3" s="78"/>
-      <c r="G3" s="79"/>
+      <c r="B3" s="78" t="s">
+        <v>49</v>
+      </c>
+      <c r="C3" s="79"/>
+      <c r="D3" s="79"/>
+      <c r="E3" s="79"/>
+      <c r="F3" s="79"/>
+      <c r="G3" s="80"/>
     </row>
     <row r="4" spans="1:7" s="3" customFormat="1" ht="38.700000000000003" customHeight="1" thickTop="1">
       <c r="A4" s="2"/>
-      <c r="B4" s="65" t="s">
+      <c r="B4" s="66" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="66"/>
+      <c r="C4" s="67"/>
       <c r="E4" s="4" t="s">
         <v>21</v>
       </c>
@@ -3507,10 +3507,10 @@
     </row>
     <row r="5" spans="1:7" ht="38.700000000000003" customHeight="1">
       <c r="A5" s="2"/>
-      <c r="B5" s="58" t="s">
+      <c r="B5" s="59" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="59"/>
+      <c r="C5" s="60"/>
       <c r="D5" s="7"/>
       <c r="E5" s="8" t="s">
         <v>22</v>
@@ -3537,10 +3537,10 @@
     </row>
     <row r="7" spans="1:7" ht="38.700000000000003" customHeight="1">
       <c r="A7" s="2"/>
-      <c r="B7" s="58" t="s">
+      <c r="B7" s="59" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="59"/>
+      <c r="C7" s="60"/>
       <c r="D7" s="14"/>
       <c r="E7" s="17" t="s">
         <v>24</v>
@@ -3550,10 +3550,10 @@
     </row>
     <row r="8" spans="1:7" ht="38.700000000000003" customHeight="1">
       <c r="A8" s="2"/>
-      <c r="B8" s="58" t="s">
+      <c r="B8" s="59" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="59"/>
+      <c r="C8" s="60"/>
       <c r="D8" s="14"/>
       <c r="E8" s="17" t="s">
         <v>25</v>
@@ -3563,28 +3563,28 @@
     </row>
     <row r="9" spans="1:7" ht="38.700000000000003" customHeight="1">
       <c r="A9" s="2"/>
-      <c r="B9" s="58" t="s">
+      <c r="B9" s="59" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="59"/>
+      <c r="C9" s="60"/>
       <c r="D9" s="19"/>
-      <c r="E9" s="60" t="s">
+      <c r="E9" s="61" t="s">
         <v>26</v>
       </c>
-      <c r="F9" s="61"/>
+      <c r="F9" s="62"/>
       <c r="G9" s="10"/>
     </row>
     <row r="10" spans="1:7" ht="38.700000000000003" customHeight="1">
       <c r="A10" s="2"/>
-      <c r="B10" s="58" t="s">
+      <c r="B10" s="59" t="s">
         <v>10</v>
       </c>
-      <c r="C10" s="59"/>
+      <c r="C10" s="60"/>
       <c r="D10" s="20"/>
-      <c r="E10" s="58" t="s">
+      <c r="E10" s="59" t="s">
         <v>11</v>
       </c>
-      <c r="F10" s="59"/>
+      <c r="F10" s="60"/>
       <c r="G10" s="10"/>
     </row>
     <row r="11" spans="1:7" ht="38.700000000000003" customHeight="1">
@@ -3592,61 +3592,61 @@
       <c r="B11" s="48" t="s">
         <v>20</v>
       </c>
-      <c r="C11" s="81" t="s">
-        <v>49</v>
+      <c r="C11" s="52" t="s">
+        <v>48</v>
       </c>
       <c r="D11" s="21"/>
-      <c r="E11" s="62"/>
-      <c r="F11" s="63"/>
-      <c r="G11" s="64"/>
+      <c r="E11" s="63"/>
+      <c r="F11" s="64"/>
+      <c r="G11" s="65"/>
     </row>
     <row r="12" spans="1:7" ht="25.95" customHeight="1" thickBot="1">
       <c r="A12" s="2"/>
-      <c r="B12" s="71" t="s">
+      <c r="B12" s="72" t="s">
         <v>29</v>
       </c>
-      <c r="C12" s="72"/>
-      <c r="D12" s="72"/>
-      <c r="E12" s="72"/>
-      <c r="F12" s="72"/>
-      <c r="G12" s="73"/>
+      <c r="C12" s="73"/>
+      <c r="D12" s="73"/>
+      <c r="E12" s="73"/>
+      <c r="F12" s="73"/>
+      <c r="G12" s="74"/>
     </row>
     <row r="13" spans="1:7" ht="38.700000000000003" customHeight="1" thickTop="1" thickBot="1">
       <c r="A13" s="2"/>
-      <c r="B13" s="55" t="s">
+      <c r="B13" s="56" t="s">
         <v>19</v>
       </c>
-      <c r="C13" s="56"/>
-      <c r="D13" s="56"/>
-      <c r="E13" s="56"/>
-      <c r="F13" s="56"/>
-      <c r="G13" s="57"/>
+      <c r="C13" s="57"/>
+      <c r="D13" s="57"/>
+      <c r="E13" s="57"/>
+      <c r="F13" s="57"/>
+      <c r="G13" s="58"/>
     </row>
     <row r="14" spans="1:7" ht="31.5" customHeight="1" thickTop="1" thickBot="1">
-      <c r="B14" s="67" t="s">
+      <c r="B14" s="68" t="s">
         <v>12</v>
       </c>
-      <c r="C14" s="68"/>
+      <c r="C14" s="69"/>
       <c r="D14" s="22"/>
       <c r="E14" s="40" t="s">
         <v>13</v>
       </c>
       <c r="F14" s="44" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G14" s="23"/>
     </row>
     <row r="15" spans="1:7" ht="31.5" customHeight="1" thickTop="1">
-      <c r="B15" s="69" t="s">
+      <c r="B15" s="70" t="s">
         <v>14</v>
       </c>
-      <c r="C15" s="70"/>
+      <c r="C15" s="71"/>
       <c r="D15" s="24"/>
       <c r="E15" s="25" t="s">
         <v>15</v>
       </c>
       <c r="F15" s="45" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G15" s="23"/>
     </row>
@@ -3655,14 +3655,14 @@
         <v>33</v>
       </c>
       <c r="C16" s="41" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D16" s="26"/>
       <c r="E16" s="25" t="s">
         <v>16</v>
       </c>
       <c r="F16" s="46" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G16" s="14"/>
     </row>
@@ -3671,40 +3671,40 @@
         <v>32</v>
       </c>
       <c r="C17" s="41" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D17" s="27"/>
       <c r="E17" s="28" t="s">
         <v>31</v>
       </c>
       <c r="F17" s="47" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G17" s="29"/>
     </row>
     <row r="18" spans="2:7" ht="28.95" customHeight="1" thickTop="1" thickBot="1">
-      <c r="B18" s="74" t="s">
+      <c r="B18" s="75" t="s">
         <v>27</v>
       </c>
-      <c r="C18" s="75"/>
-      <c r="D18" s="75"/>
-      <c r="E18" s="75"/>
-      <c r="F18" s="75"/>
-      <c r="G18" s="76"/>
+      <c r="C18" s="76"/>
+      <c r="D18" s="76"/>
+      <c r="E18" s="76"/>
+      <c r="F18" s="76"/>
+      <c r="G18" s="77"/>
     </row>
     <row r="19" spans="2:7" ht="31.5" customHeight="1" thickTop="1">
       <c r="B19" s="51" t="s">
         <v>17</v>
       </c>
       <c r="C19" s="41" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D19" s="27"/>
       <c r="E19" s="50" t="s">
         <v>0</v>
       </c>
       <c r="F19" s="41" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G19" s="30"/>
     </row>
@@ -3713,7 +3713,7 @@
         <v>18</v>
       </c>
       <c r="C20" s="43" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D20" s="31"/>
       <c r="E20" s="32"/>
@@ -3783,13 +3783,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="22.5" customHeight="1" thickBot="1">
-      <c r="A1" s="80" t="s">
+      <c r="A1" s="81" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="80"/>
-      <c r="C1" s="80"/>
-      <c r="D1" s="80"/>
-      <c r="E1" s="80"/>
+      <c r="B1" s="81"/>
+      <c r="C1" s="81"/>
+      <c r="D1" s="81"/>
+      <c r="E1" s="81"/>
     </row>
     <row r="2" spans="1:5" ht="27.6" thickTop="1">
       <c r="A2" s="36" t="s">
